--- a/生物化学实验(Biochemistry Lab)/Week 8/实验报告/标准曲线.xlsx
+++ b/生物化学实验(Biochemistry Lab)/Week 8/实验报告/标准曲线.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/peiyuliu/Desktop/PKU-Undergraduate-Course-Public/生物化学实验(Biochemistry Lab)/Week 8/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/peiyuliu/Desktop/PKU-Undergraduate-Course-Public/生物化学实验(Biochemistry Lab)/Week 8/实验报告/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7E333C-6C39-EB49-AA6C-BD8B2AFDD050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F6BF34-08A7-C944-AFD1-C27BC09F1FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17780" xr2:uid="{14AFD0F3-D03E-8D42-8E11-574D8C5C3EE4}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17760" xr2:uid="{14AFD0F3-D03E-8D42-8E11-574D8C5C3EE4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -291,7 +291,7 @@
                 </a:r>
                 <a:r>
                   <a:rPr lang="en-US" sz="700"/>
-                  <a:t>r</a:t>
+                  <a:t>R</a:t>
                 </a:r>
                 <a:endParaRPr lang="en-US"/>
               </a:p>
@@ -3699,7 +3699,7 @@
         <v>718.18</v>
       </c>
       <c r="C35">
-        <f t="shared" ref="C35:C41" si="4">A35/B35</f>
+        <f t="shared" ref="C35:C38" si="4">A35/B35</f>
         <v>0.14664847252777855</v>
       </c>
       <c r="D35">
